--- a/scripts/reflect/changed.xlsx
+++ b/scripts/reflect/changed.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Scratch" sheetId="3" r:id="rId3"/>
     <sheet name="Q1 Data" sheetId="5" r:id="rId5"/>
     <sheet name="It's" sheetId="6" r:id="rId6"/>
-    <sheet name="Audit" sheetId="7" r:id="rId11"/>
+    <sheet name="Review" sheetId="7" r:id="rId11"/>
+    <sheet name="Audit" sheetId="8" r:id="rId12"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
@@ -394,6 +395,88 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1">
+        <v>10</v>
+      </c>
+      <c r="B1">
+        <f>A1*2</f>
+        <v>20</v>
+      </c>
+      <c r="C1">
+        <f>A1+1</f>
+        <v>11</v>
+      </c>
+      <c r="D1">
+        <f>Z9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <f>A2*2</f>
+        <v>40</v>
+      </c>
+      <c r="C2">
+        <f>A2+1</f>
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <f>Model!H1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>61</v>
+      </c>
+      <c r="C3">
+        <f>A3+2</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>40</v>
+      </c>
+      <c r="B4">
+        <f>A4*2</f>
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <f>A4+1</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <f>A5*2</f>
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <f>A5+1</f>
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
